--- a/diseases/d242/2020-2025.xlsx
+++ b/diseases/d242/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>7</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.1301290964290996</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.03717974183688559</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.05576961275532839</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.03717974183688559</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.05547244447924827</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>3</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.05547244447924827</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.01849081482641609</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>2</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.03698162965283218</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.01849081482641609</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>5</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.09162876824454766</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>5</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.09162876824454766</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>3</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.05497726094672859</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>5</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.09162876824454766</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>2</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.03665150729781906</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>6</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.1099545218934572</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>2</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.03665150729781906</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>3</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.05497726094672859</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>3</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.05497726094672859</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>4</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.07247470496906508</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.01811867624226627</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.01811867624226627</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>4</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.07247470496906508</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>2</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.03623735248453254</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>4</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.07247470496906508</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>4</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.07247470496906508</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>2</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.03623735248453254</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>6</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.1087120574535976</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>4</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.07247470496906508</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>5</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.09059338121133134</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>7</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.1268307336958639</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>4</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.07172752149135864</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>3</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.05379564111851897</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.01793188037283966</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>3</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.05379564111851897</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>4</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.07172752149135864</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>2</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.03586376074567932</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>6</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.1075912822370379</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>5</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.08965940186419828</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.05379564111851897</v>
       </c>
@@ -24129,9 +23952,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -24525,9 +24345,6 @@
       <c r="O122" t="n">
         <v>5</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.08891938230906209</v>
       </c>
@@ -24921,9 +24738,6 @@
       <c r="O124" t="n">
         <v>5</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.08891938230906209</v>
       </c>
@@ -25317,9 +25131,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.01778387646181242</v>
       </c>
@@ -25713,9 +25524,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -26109,9 +25917,6 @@
       <c r="O130" t="n">
         <v>4</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.07113550584724966</v>
       </c>
@@ -26505,9 +26310,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -26901,9 +26703,6 @@
       <c r="O134" t="n">
         <v>8</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.1422710116944993</v>
       </c>
@@ -27297,9 +27096,6 @@
       <c r="O136" t="n">
         <v>6</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.1067032587708745</v>
       </c>
@@ -27693,9 +27489,6 @@
       <c r="O138" t="n">
         <v>3</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.05335162938543725</v>
       </c>
@@ -28089,9 +27882,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.01778387646181242</v>
       </c>
@@ -28485,9 +28275,6 @@
       <c r="O142" t="n">
         <v>3</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.05335162938543725</v>
       </c>
@@ -28880,9 +28667,6 @@
       </c>
       <c r="O144" t="n">
         <v>1</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>0.01778387646181242</v>

--- a/diseases/d242/2020-2025.xlsx
+++ b/diseases/d242/2020-2025.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>165</v>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>165</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1301290964290996</v>
+        <v>0.2503593130307357</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -775,12 +775,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -813,42 +813,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -919,29 +919,29 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>165</v>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>165</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Lymfogranuloma venerum (LGV)</t>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1047,42 +1047,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1144,22 +1144,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2020-02</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03717974183688559</v>
+        <v>0.1301290964290996</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1303,19 +1303,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2020-02</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1537,22 +1537,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2020-02</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>0.05576961275532839</v>
+        <v>0.03717974183688559</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1696,19 +1696,19 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2020-02</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1930,22 +1930,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.05576961275532839</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -2089,19 +2089,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2323,22 +2323,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2020-05</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03717974183688559</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2482,19 +2482,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2020-05</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2716,22 +2716,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-05</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.03717974183688559</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2875,19 +2875,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-05</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2020-10</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2020-10</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2020-10</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2020-10</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5860,22 +5860,22 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>0.2617898199245433</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5922,42 +5922,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5989,12 +5989,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -6019,38 +6019,38 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Lymfogranuloma venerum (LGV)</t>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6110,17 +6110,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -6156,42 +6156,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6253,12 +6253,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2021-03</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2021-03</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-03</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-03</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -7825,22 +7825,22 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.05547244447924827</v>
+        <v>0</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -7984,19 +7984,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -8218,22 +8218,22 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.05547244447924827</v>
+        <v>0</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -8377,19 +8377,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -8611,22 +8611,22 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2021-09</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01849081482641609</v>
+        <v>0.05547244447924827</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8770,19 +8770,19 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2021-09</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -9004,22 +9004,22 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.05547244447924827</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -9163,19 +9163,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -9397,22 +9397,22 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03698162965283218</v>
+        <v>0.01849081482641609</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -9556,19 +9556,19 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -9790,22 +9790,22 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.01849081482641609</v>
+        <v>0</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9949,19 +9949,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -10183,22 +10183,22 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>0.09162876824454766</v>
+        <v>0.03698162965283218</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -10342,19 +10342,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -10576,22 +10576,22 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>0.09162876824454766</v>
+        <v>0.01849081482641609</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10735,19 +10735,19 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -10939,12 +10939,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10969,22 +10969,22 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="O54" t="n">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="R54" t="n">
-        <v>0.05497726094672859</v>
+        <v>0.2972355203055351</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10993,12 +10993,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -11031,42 +11031,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11098,12 +11098,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11128,38 +11128,38 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="O55" t="n">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Lymfogranuloma venerum (LGV)</t>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11219,17 +11219,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -11265,42 +11265,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11362,12 +11362,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -11521,12 +11521,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -11755,22 +11755,22 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>0.01832575364890953</v>
+        <v>0.09162876824454766</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11914,19 +11914,19 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -12148,22 +12148,22 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>0.01832575364890953</v>
+        <v>0.05497726094672859</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12307,19 +12307,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -12541,22 +12541,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>0.09162876824454766</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12700,19 +12700,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -12934,22 +12934,22 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>0.03665150729781906</v>
+        <v>0.01832575364890953</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13093,19 +13093,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13327,22 +13327,22 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>0.1099545218934572</v>
+        <v>0.01832575364890953</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13486,19 +13486,19 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13720,22 +13720,22 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03665150729781906</v>
+        <v>0</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13879,19 +13879,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -14113,22 +14113,22 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>0.05497726094672859</v>
+        <v>0.03665150729781906</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -14272,19 +14272,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -14506,22 +14506,22 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R72" t="n">
-        <v>0.05497726094672859</v>
+        <v>0.1099545218934572</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14665,19 +14665,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -14899,22 +14899,22 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>0.07247470496906508</v>
+        <v>0.03665150729781906</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -15058,19 +15058,19 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15292,22 +15292,22 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>0.01811867624226627</v>
+        <v>0.05497726094672859</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15451,19 +15451,19 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15685,22 +15685,22 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01811867624226627</v>
+        <v>0.05497726094672859</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15844,19 +15844,19 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -16048,12 +16048,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -16078,22 +16078,22 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c r="R80" t="n">
-        <v>0.07247470496906508</v>
+        <v>0.1821224343803085</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -16102,12 +16102,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -16140,42 +16140,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -16207,12 +16207,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -16237,38 +16237,38 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Lymfogranuloma venerum (LGV)</t>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -16374,42 +16374,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -16471,22 +16471,22 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R82" t="n">
-        <v>0.03623735248453254</v>
+        <v>0.07247470496906508</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -16630,19 +16630,19 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -16864,22 +16864,22 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>0.07247470496906508</v>
+        <v>0.01811867624226627</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -17023,19 +17023,19 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -17257,22 +17257,22 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>0.07247470496906508</v>
+        <v>0.01811867624226627</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17416,19 +17416,19 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -17650,22 +17650,22 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R88" t="n">
-        <v>0.03623735248453254</v>
+        <v>0.07247470496906508</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -17809,19 +17809,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -18043,22 +18043,22 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O90" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R90" t="n">
-        <v>0.1087120574535976</v>
+        <v>0.03623735248453254</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -18202,19 +18202,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -18436,12 +18436,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -18595,12 +18595,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -18829,22 +18829,22 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R94" t="n">
-        <v>0.09059338121133134</v>
+        <v>0.07247470496906508</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18988,19 +18988,19 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -19222,22 +19222,22 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>0.1268307336958639</v>
+        <v>0.03623735248453254</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -19381,19 +19381,19 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O97" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -19615,22 +19615,22 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R98" t="n">
-        <v>0.07172752149135864</v>
+        <v>0.1087120574535976</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19774,19 +19774,19 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -20008,22 +20008,22 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>0.05379564111851897</v>
+        <v>0.07247470496906508</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -20167,19 +20167,19 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -20401,22 +20401,22 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R102" t="n">
-        <v>0.01793188037283966</v>
+        <v>0.09059338121133134</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -20560,19 +20560,19 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -20794,22 +20794,22 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O104" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R104" t="n">
-        <v>0.05379564111851897</v>
+        <v>0.1268307336958639</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20953,19 +20953,19 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O105" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -21157,12 +21157,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -21187,22 +21187,22 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>195</v>
       </c>
       <c r="O106" t="n">
-        <v>4</v>
+        <v>195</v>
       </c>
       <c r="R106" t="n">
-        <v>0.07172752149135864</v>
+        <v>0.2930192425511184</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -21211,12 +21211,12 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -21249,42 +21249,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21316,12 +21316,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -21346,38 +21346,38 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>4</v>
+        <v>195</v>
       </c>
       <c r="O107" t="n">
-        <v>4</v>
+        <v>195</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Lymfogranuloma venerum (LGV)</t>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -21387,12 +21387,12 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -21437,17 +21437,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -21483,42 +21483,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -21580,22 +21580,22 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R108" t="n">
-        <v>0.03586376074567932</v>
+        <v>0.07172752149135864</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21739,19 +21739,19 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -21973,22 +21973,22 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>0.05379564111851897</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -22132,19 +22132,19 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -22366,22 +22366,22 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>0.1075912822370379</v>
+        <v>0.01793188037283966</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -22525,19 +22525,19 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -22759,22 +22759,22 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>0.08965940186419828</v>
+        <v>0.05379564111851897</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22918,19 +22918,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -23152,22 +23152,22 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>0.07172752149135864</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -23311,19 +23311,19 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -23545,22 +23545,22 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R118" t="n">
-        <v>0.05379564111851897</v>
+        <v>0.03586376074567932</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -23704,19 +23704,19 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -23938,12 +23938,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -24097,12 +24097,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -24331,22 +24331,22 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="N122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R122" t="n">
-        <v>0.08891938230906209</v>
+        <v>0.1075912822370379</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -24490,19 +24490,19 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="N123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -24724,12 +24724,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="N124" t="n">
@@ -24739,7 +24739,7 @@
         <v>5</v>
       </c>
       <c r="R124" t="n">
-        <v>0.08891938230906209</v>
+        <v>0.08965940186419828</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -24883,12 +24883,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="N125" t="n">
@@ -25117,22 +25117,22 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0.01778387646181242</v>
+        <v>0</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -25276,19 +25276,19 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -25510,22 +25510,22 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>0.05379564111851897</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -25669,19 +25669,19 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -25903,22 +25903,22 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0.07113550584724966</v>
+        <v>0</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -26062,19 +26062,19 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -26296,22 +26296,22 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>0.08891938230906209</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -26455,19 +26455,19 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -26689,22 +26689,22 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O134" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R134" t="n">
-        <v>0.1422710116944993</v>
+        <v>0.08891938230906209</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -26848,19 +26848,19 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O135" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -27082,22 +27082,22 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N136" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O136" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R136" t="n">
-        <v>0.1067032587708745</v>
+        <v>0.01778387646181242</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -27241,19 +27241,19 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N137" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O137" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -27475,22 +27475,22 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0.05335162938543725</v>
+        <v>0</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -27634,19 +27634,19 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -27868,22 +27868,22 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R140" t="n">
-        <v>0.01778387646181242</v>
+        <v>0.07113550584724966</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -28027,19 +28027,19 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -28261,22 +28261,22 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>0.05335162938543725</v>
+        <v>0</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -28420,19 +28420,19 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="N143" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -28654,22 +28654,22 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O144" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R144" t="n">
-        <v>0.01778387646181242</v>
+        <v>0.1422710116944993</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -28813,19 +28813,19 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O145" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
@@ -28984,6 +28984,1971 @@
         </is>
       </c>
       <c r="BC145" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>6</v>
+      </c>
+      <c r="O146" t="n">
+        <v>6</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.1067032587708745</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>6</v>
+      </c>
+      <c r="O147" t="n">
+        <v>6</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN147" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>3</v>
+      </c>
+      <c r="O148" t="n">
+        <v>3</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.05335162938543725</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>3</v>
+      </c>
+      <c r="O149" t="n">
+        <v>3</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" t="n">
+        <v>1</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.01778387646181242</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>3</v>
+      </c>
+      <c r="O152" t="n">
+        <v>3</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0.05335162938543725</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>3</v>
+      </c>
+      <c r="O153" t="n">
+        <v>3</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>1</v>
+      </c>
+      <c r="O154" t="n">
+        <v>1</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0.01778387646181242</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" t="n">
+        <v>1</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -29105,7 +31070,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -29115,7 +31080,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -29135,7 +31100,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -29145,7 +31110,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -29167,7 +31132,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>172</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="16">
